--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104739_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104739_W32.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0841</v>
+        <v>5.9654</v>
       </c>
       <c r="E2" t="n">
-        <v>3.319</v>
+        <v>3.5519</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7651</v>
+        <v>2.4134</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0823</v>
+        <v>4.0797</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0766</v>
+        <v>0.0825</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0057</v>
+        <v>3.9973</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6101</v>
+        <v>4.5962</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2788</v>
+        <v>1.2755</v>
       </c>
       <c r="L2" t="n">
-        <v>3.3313</v>
+        <v>3.3206</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5278</v>
+        <v>-0.5164</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2022</v>
+        <v>-1.1931</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6744</v>
+        <v>0.6766</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9534</v>
+        <v>-2.9592</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6335</v>
+        <v>0.5181</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0254</v>
+        <v>0.2808</v>
       </c>
       <c r="U2" t="n">
-        <v>0.608</v>
+        <v>0.2374</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3683</v>
+        <v>1.3675</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2685</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2627</v>
+        <v>4.8062</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3026</v>
+        <v>3.0566</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9601</v>
+        <v>1.7496</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5595</v>
+        <v>3.5553</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3825</v>
+        <v>1.3789</v>
       </c>
       <c r="I3" t="n">
-        <v>2.177</v>
+        <v>2.1764</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8608</v>
+        <v>2.8523</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6305</v>
+        <v>1.6235</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2303</v>
+        <v>1.2288</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6987</v>
+        <v>0.703</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.248</v>
+        <v>-0.2446</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9467</v>
+        <v>0.9476</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0217</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4419</v>
+        <v>0.2042</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5798</v>
+        <v>0.3637</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7083</v>
+        <v>4.1254</v>
       </c>
       <c r="E4" t="n">
-        <v>2.466</v>
+        <v>2.7231</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2423</v>
+        <v>1.4023</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8149999999999999</v>
+        <v>4.9508</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4275</v>
+        <v>0.7058</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3875</v>
+        <v>4.245</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5614</v>
+        <v>5.0066</v>
       </c>
       <c r="K4" t="n">
-        <v>0.375</v>
+        <v>1.2238</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1864</v>
+        <v>3.7828</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2536</v>
+        <v>-0.0558</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0526</v>
+        <v>-0.518</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2011</v>
+        <v>0.4622</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1359</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4078</v>
+        <v>-4.0974</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3931</v>
+        <v>0.5598</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0386</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3545</v>
+        <v>-0.1645</v>
       </c>
       <c r="V4" t="n">
-        <v>2.6361</v>
+        <v>0.4358</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2738</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2734</v>
+        <v>3.4076</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2027</v>
+        <v>1.3328</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0707</v>
+        <v>2.0748</v>
       </c>
       <c r="G5" t="n">
-        <v>4.951</v>
+        <v>0.8143</v>
       </c>
       <c r="H5" t="n">
-        <v>0.701</v>
+        <v>0.4253</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2501</v>
+        <v>0.389</v>
       </c>
       <c r="J5" t="n">
-        <v>5.0177</v>
+        <v>0.5547</v>
       </c>
       <c r="K5" t="n">
-        <v>1.227</v>
+        <v>0.3685</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7907</v>
+        <v>0.1862</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.2597</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.526</v>
+        <v>0.0568</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4594</v>
+        <v>0.2028</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8175</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.0894</v>
+        <v>-3.4145</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2966</v>
+        <v>1.094</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1832</v>
+        <v>0.9242</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4798</v>
+        <v>0.1699</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4365</v>
+        <v>2.6374</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0913</v>
+        <v>3.2684</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6548</v>
+        <v>-0.6311</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. BROOKS</t>
+          <t>R. OBASOHAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6107</v>
+        <v>2.8787</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7234</v>
+        <v>0.3833</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8872</v>
+        <v>2.4954</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8328</v>
+        <v>3.0207</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3907</v>
+        <v>3.1427</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2235</v>
+        <v>-0.122</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2854</v>
+        <v>3.1924</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4208</v>
+        <v>3.8331</v>
       </c>
       <c r="L6" t="n">
-        <v>2.8647</v>
+        <v>-0.6407</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4527</v>
+        <v>-0.1717</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8115</v>
+        <v>-0.6904</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3588</v>
+        <v>0.5187</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2272</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.7262</v>
+        <v>-2.9592</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4991</v>
+        <v>3.6421</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0051</v>
+        <v>-0.6445</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1642</v>
+        <v>-0.3232</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1592</v>
+        <v>-0.3213</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.1804</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.4733</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. UBAL</t>
+          <t>E. BROOKS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4678</v>
+        <v>2.6302</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8621</v>
+        <v>0.5401</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6057</v>
+        <v>2.0902</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4069</v>
+        <v>2.8323</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.3881</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7916</v>
+        <v>3.2203</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.6155</v>
+        <v>3.2765</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9384</v>
+        <v>0.4169</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6771</v>
+        <v>2.8596</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2085</v>
+        <v>-0.4442</v>
       </c>
       <c r="N7" t="n">
-        <v>0.323</v>
+        <v>-0.805</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1145</v>
+        <v>0.3608</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2719</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2272</v>
+        <v>-2.7316</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4613</v>
+        <v>0.0256</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2716</v>
+        <v>-0.0049</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1897</v>
+        <v>0.0305</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1415</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.4332</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. OBASOHAN</t>
+          <t>A. UBAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1754</v>
+        <v>2.2612</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0804</v>
+        <v>1.7297</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2558</v>
+        <v>0.5315</v>
       </c>
       <c r="G8" t="n">
-        <v>3.0265</v>
+        <v>-1.4031</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1497</v>
+        <v>-0.6121</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1232</v>
+        <v>-0.791</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2087</v>
+        <v>-1.6195</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8485</v>
+        <v>-0.9415</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6398</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1822</v>
+        <v>0.2164</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6988</v>
+        <v>0.3294</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5165999999999999</v>
+        <v>-0.113</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6816</v>
+        <v>2.2763</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9534</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>3.635</v>
+        <v>2.5039</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3562</v>
+        <v>0.2497</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8139</v>
+        <v>0.1506</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5423</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1765</v>
+        <v>1.1383</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4782</v>
+        <v>3.4262</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6548</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.074</v>
+        <v>0.3085</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.02</v>
+        <v>-3.0329</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9459</v>
+        <v>3.3414</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1049</v>
+        <v>-2.1054</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2029</v>
+        <v>-0.2012</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.902</v>
+        <v>-1.9041</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.8562</v>
+        <v>-2.8652</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1503</v>
+        <v>0.1444</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.0065</v>
+        <v>-3.0096</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7513</v>
+        <v>0.7598</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3532</v>
+        <v>-0.3457</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1045</v>
+        <v>1.1055</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1869</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0634</v>
+        <v>0.06</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1236</v>
+        <v>0.5021</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4279</v>
+        <v>-0.4245</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4279</v>
+        <v>-0.4245</v>
       </c>
     </row>
     <row r="10">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8835</v>
+        <v>-0.493</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5882</v>
+        <v>-2.8742</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7047</v>
+        <v>2.3812</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0863</v>
+        <v>-0.0832</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9437</v>
+        <v>-0.9396</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8575</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2659</v>
+        <v>0.2596</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9211</v>
+        <v>-0.9243</v>
       </c>
       <c r="L10" t="n">
-        <v>1.187</v>
+        <v>1.1839</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3521</v>
+        <v>-0.3428</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0226</v>
+        <v>-0.0154</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3295</v>
+        <v>-0.3275</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>3.4078</v>
+        <v>3.4145</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7972</v>
+        <v>-0.4098</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6057</v>
+        <v>0.1228</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1915</v>
+        <v>-0.5326</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. PEREZ</t>
+          <t>D. DUKE JR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9748</v>
+        <v>-1.7185</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0447</v>
+        <v>-1.8452</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0699</v>
+        <v>0.1267</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8291</v>
+        <v>-2.14</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.387</v>
+        <v>-1.9385</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4421</v>
+        <v>-0.2015</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3059</v>
+        <v>-2.1981</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9211</v>
+        <v>-2.3689</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3848</v>
+        <v>0.1708</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5231</v>
+        <v>0.0581</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4659</v>
+        <v>0.4305</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0573</v>
+        <v>-0.3724</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4991</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3729</v>
+        <v>0.1939</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4669</v>
+        <v>0.3529</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0939</v>
+        <v>-0.159</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. DUKE JR</t>
+          <t>D. PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2826</v>
+        <v>-1.7626</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3121</v>
+        <v>-3.9393</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0295</v>
+        <v>2.1767</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1369</v>
+        <v>-1.8288</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9385</v>
+        <v>-1.3845</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1984</v>
+        <v>-0.4442</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.1923</v>
+        <v>-1.312</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.3667</v>
+        <v>-0.9243</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1744</v>
+        <v>-0.3877</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0554</v>
+        <v>-0.5168</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4282</v>
+        <v>-0.4603</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3728</v>
+        <v>-0.0565</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2272</v>
+        <v>2.5039</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3729</v>
+        <v>-0.1615</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1198</v>
+        <v>-0.351</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2531</v>
+        <v>0.1895</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.459</v>
+        <v>-2.8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1616</v>
+        <v>-0.1322</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6207</v>
+        <v>-2.6678</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1861</v>
+        <v>-1.1795</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7101</v>
+        <v>-0.7044</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.476</v>
+        <v>-0.4751</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1983</v>
+        <v>0.1979</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0864</v>
+        <v>0.0862</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1118</v>
+        <v>0.1117</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3843</v>
+        <v>-1.3774</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7965</v>
+        <v>-0.7906</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5878</v>
+        <v>-0.5868</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.5903</v>
+        <v>-1.5934</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0227</v>
+        <v>-0.3717</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3031</v>
+        <v>0.0161</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3257</v>
+        <v>-0.3878</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4775</v>
+        <v>-1.4764</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.7281</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.9085</v>
+        <v>19.60910000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9920000000000009</v>
+        <v>1.493700000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>17.9162</v>
+        <v>18.1154</v>
       </c>
       <c r="G14" t="n">
-        <v>10.5169</v>
+        <v>10.5131</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4509999999999998</v>
+        <v>-0.4331999999999997</v>
       </c>
       <c r="I14" t="n">
-        <v>10.968</v>
+        <v>10.9465</v>
       </c>
       <c r="J14" t="n">
-        <v>12.0384</v>
+        <v>11.9414</v>
       </c>
       <c r="K14" t="n">
-        <v>3.870000000000001</v>
+        <v>3.8129</v>
       </c>
       <c r="L14" t="n">
-        <v>8.1684</v>
+        <v>8.128499999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5213</v>
+        <v>-1.4281</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.3209</v>
+        <v>-4.2464</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7996</v>
+        <v>2.818</v>
       </c>
       <c r="P14" t="n">
-        <v>3.408</v>
+        <v>3.4143</v>
       </c>
       <c r="Q14" t="n">
-        <v>-23.85459999999999</v>
+        <v>-23.9013</v>
       </c>
       <c r="R14" t="n">
-        <v>27.2627</v>
+        <v>27.3156</v>
       </c>
       <c r="S14" t="n">
-        <v>1.483099999999999</v>
+        <v>2.1836</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4851</v>
+        <v>2.1568</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.002099999999999991</v>
+        <v>0.02699999999999997</v>
       </c>
       <c r="V14" t="n">
-        <v>3.5005</v>
+        <v>3.4977</v>
       </c>
       <c r="W14" t="n">
-        <v>11.3235</v>
+        <v>11.2966</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.822699999999999</v>
+        <v>-7.7991</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1242</v>
+        <v>2.2867</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3255</v>
+        <v>1.592</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7987</v>
+        <v>0.6947</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2836</v>
+        <v>1.6999</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1638</v>
+        <v>1.1516</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1198</v>
+        <v>0.5483</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0864</v>
+        <v>2.0707</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4899</v>
+        <v>0.8791</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5965</v>
+        <v>1.1916</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.37</v>
+        <v>-0.3708</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6536999999999999</v>
+        <v>0.2725</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7163</v>
+        <v>-0.6433</v>
       </c>
       <c r="P15" t="n">
+        <v>0.9105</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.1382</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.008200000000000001</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.251</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.2429</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.3155</v>
+      </c>
+      <c r="W15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-2.7262</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.7262</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.476</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.7829</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.6932</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.9318</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.1825</v>
-      </c>
       <c r="X15" t="n">
-        <v>-1.2507</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8561</v>
+        <v>1.4434</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3613</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4948</v>
+        <v>0.6083</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6997</v>
+        <v>-0.2768</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1518</v>
+        <v>-0.1612</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5479000000000001</v>
+        <v>-0.1156</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0743</v>
+        <v>1.0817</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8813</v>
+        <v>0.4859</v>
       </c>
       <c r="L16" t="n">
-        <v>1.193</v>
+        <v>0.5958</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3746</v>
+        <v>-1.3585</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2705</v>
+        <v>-0.6471</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6451</v>
+        <v>-0.7114</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9087</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2272</v>
+        <v>-2.7316</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1359</v>
+        <v>2.7316</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4336</v>
+        <v>0.7885</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4858</v>
+        <v>0.3061</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0523</v>
+        <v>0.4824</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3188</v>
+        <v>0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3188</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5074</v>
+        <v>1.2108</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8838</v>
+        <v>2.5019</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3764</v>
+        <v>-1.2911</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4681</v>
+        <v>-0.472</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1743</v>
+        <v>0.17</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6424</v>
+        <v>-0.642</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2787</v>
+        <v>2.263</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9859</v>
+        <v>0.975</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2929</v>
+        <v>1.288</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7468</v>
+        <v>-2.735</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8115</v>
+        <v>-0.805</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.9353</v>
+        <v>-1.93</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4298</v>
+        <v>0.1381</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9217</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4918</v>
+        <v>-0.4259</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0119</v>
+        <v>0.1367</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4536</v>
+        <v>0.5607</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4655</v>
+        <v>-0.424</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0557</v>
+        <v>1.0542</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3479</v>
+        <v>1.3445</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2923</v>
+        <v>-0.2902</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4604</v>
+        <v>1.4539</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4231</v>
+        <v>1.4167</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4047</v>
+        <v>-0.3997</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0752</v>
+        <v>-0.0722</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3295</v>
+        <v>-0.3275</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2947</v>
+        <v>-0.1451</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4164</v>
+        <v>-0.2998</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1217</v>
+        <v>0.1546</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.243</v>
+        <v>-0.4444</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6168</v>
+        <v>-0.8613</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3738</v>
+        <v>0.4168</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1427</v>
+        <v>-1.1375</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7386</v>
+        <v>-0.7356</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4041</v>
+        <v>-0.4019</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0377</v>
+        <v>0.0358</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6334</v>
+        <v>-0.6345</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6711</v>
+        <v>0.6703</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1804</v>
+        <v>-1.1733</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1052</v>
+        <v>-0.1011</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0752</v>
+        <v>-1.0722</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0588</v>
+        <v>-0.1476</v>
       </c>
       <c r="T19" t="n">
-        <v>0.322</v>
+        <v>0.0834</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2633</v>
+        <v>-0.2309</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. WASHINGTON</t>
+          <t>T. BELL-HAYNES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5899</v>
+        <v>-0.8405</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8184</v>
+        <v>-1.5703</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2285</v>
+        <v>0.7298</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7083</v>
+        <v>2.8878</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.6883</v>
+        <v>1.7926</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.02</v>
+        <v>1.0952</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.2603</v>
+        <v>3.5148</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.2976</v>
+        <v>1.7647</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>1.7501</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.448</v>
+        <v>-0.627</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3907</v>
+        <v>0.028</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0573</v>
+        <v>-0.6549</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9087</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-5.0079</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9087</v>
+        <v>2.5039</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2096</v>
+        <v>-0.2927</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4419</v>
+        <v>-0.2349</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2323</v>
+        <v>-0.0578</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. BELL-HAYNES</t>
+          <t>I. WASHINGTON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7824</v>
+        <v>-1.7783</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8985</v>
+        <v>-2.2954</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1161</v>
+        <v>0.5171</v>
       </c>
       <c r="G21" t="n">
-        <v>2.8904</v>
+        <v>-2.7073</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7973</v>
+        <v>-2.688</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0931</v>
+        <v>-0.0193</v>
       </c>
       <c r="J21" t="n">
-        <v>3.527</v>
+        <v>-2.2627</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7748</v>
+        <v>-2.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7522</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.4446</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0225</v>
+        <v>-0.3881</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6591</v>
+        <v>-0.0565</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4991</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.9981</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4991</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2419</v>
+        <v>0.0185</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5867</v>
+        <v>-0.0327</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6552</v>
+        <v>0.0512</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9318</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1594</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7895</v>
+        <v>-2.9121</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7101</v>
+        <v>-1.7134</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0794</v>
+        <v>-1.1987</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2804</v>
+        <v>-1.2791</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7671</v>
+        <v>-0.7668</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5133</v>
+        <v>-0.5123</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6625</v>
+        <v>-0.6635</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7371</v>
+        <v>-0.7379</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6179</v>
+        <v>-0.6157</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0301</v>
+        <v>-0.0289</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5878</v>
+        <v>-0.5868</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0366</v>
+        <v>-0.0882</v>
       </c>
       <c r="T22" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0882</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0518</v>
+        <v>-0.1765</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5773</v>
+        <v>-3.0386</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9009</v>
+        <v>-3.0738</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3236</v>
+        <v>0.0351</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9982</v>
+        <v>-4.121</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9355</v>
+        <v>-0.2124</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9374</v>
+        <v>-3.9086</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8526</v>
+        <v>-2.8363</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6043</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7516</v>
+        <v>-2.2945</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8545</v>
+        <v>-1.2847</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6688</v>
+        <v>0.3294</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1857</v>
+        <v>-1.6141</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.9534</v>
+        <v>1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.9069</v>
+        <v>-1.5934</v>
       </c>
       <c r="R23" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.2834</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.006</v>
+        <v>0.1087</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.3921</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1594</v>
+        <v>1.2472</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6314</v>
+        <v>-3.3316</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1727</v>
+        <v>-3.9308</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4587</v>
+        <v>0.5992</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.1237</v>
+        <v>0.997</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2119</v>
+        <v>1.9305</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.9119</v>
+        <v>-0.9335</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.827</v>
+        <v>1.8396</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5349</v>
+        <v>2.592</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.2921</v>
+        <v>-0.7524</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2967</v>
+        <v>-0.8426</v>
       </c>
       <c r="N24" t="n">
-        <v>0.323</v>
+        <v>-0.6615</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6197</v>
+        <v>-0.1811</v>
       </c>
       <c r="P24" t="n">
-        <v>1.3631</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.5903</v>
+        <v>-5.9184</v>
       </c>
       <c r="R24" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8708</v>
+        <v>-0.2799</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.006</v>
+        <v>-0.0097</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8648</v>
+        <v>-0.2702</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2507</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8134</v>
+        <v>-4.2362</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.2301</v>
+        <v>-5.0094</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4166</v>
+        <v>0.7732</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.0023</v>
+        <v>-2.0042</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.29</v>
+        <v>-0.2926</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.7123</v>
+        <v>-1.7116</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.4248</v>
+        <v>-1.4321</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1158</v>
+        <v>0.1099</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.5405</v>
+        <v>-1.542</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5775</v>
+        <v>-0.572</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4058</v>
+        <v>-0.4025</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1718</v>
+        <v>-0.1695</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.0447</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6071</v>
+        <v>-0.0256</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3975</v>
+        <v>-0.1628</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2096</v>
+        <v>0.1372</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.9573</v>
+        <v>-5.8287</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.1387</v>
+        <v>-5.6957</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1814</v>
+        <v>-0.133</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.1519</v>
+        <v>-5.1543</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.0962</v>
+        <v>-1.0994</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.0557</v>
+        <v>-4.0549</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.6212</v>
+        <v>-3.6366</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2488</v>
+        <v>0.2371</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.8699</v>
+        <v>-3.8737</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.5307</v>
+        <v>-1.5177</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.345</v>
+        <v>-1.3365</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1857</v>
+        <v>-0.1811</v>
       </c>
       <c r="P26" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R26" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="S26" t="n">
-        <v>0.285</v>
+        <v>0.4182</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6561</v>
+        <v>-0.1862</v>
       </c>
       <c r="U26" t="n">
-        <v>0.9412</v>
+        <v>0.6044</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.5449</v>
+        <v>-1.5479</v>
       </c>
       <c r="W26" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6311</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-18.9084</v>
+        <v>-17.3328</v>
       </c>
       <c r="E27" t="n">
-        <v>-18.462</v>
+        <v>-18.6603</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4465000000000001</v>
+        <v>1.3274</v>
       </c>
       <c r="G27" t="n">
-        <v>-10.517</v>
+        <v>-10.5133</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4509000000000003</v>
+        <v>0.4332000000000003</v>
       </c>
       <c r="I27" t="n">
-        <v>-10.9682</v>
+        <v>-10.9464</v>
       </c>
       <c r="J27" t="n">
-        <v>1.521300000000001</v>
+        <v>1.428300000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>4.320899999999999</v>
+        <v>4.246200000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.7992</v>
+        <v>-2.817900000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-12.0384</v>
+        <v>-11.9416</v>
       </c>
       <c r="N27" t="n">
-        <v>-3.87</v>
+        <v>-3.813</v>
       </c>
       <c r="O27" t="n">
-        <v>-8.1685</v>
+        <v>-8.128400000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>-3.4079</v>
+        <v>-3.4144</v>
       </c>
       <c r="Q27" t="n">
-        <v>-27.2624</v>
+        <v>-27.3158</v>
       </c>
       <c r="R27" t="n">
-        <v>23.85439999999999</v>
+        <v>23.9013</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.483</v>
+        <v>0.09260000000000002</v>
       </c>
       <c r="T27" t="n">
-        <v>0.002400000000000069</v>
+        <v>-0.02670000000000008</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.4851</v>
+        <v>0.1193000000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>-3.500599999999999</v>
+        <v>-3.4976</v>
       </c>
       <c r="W27" t="n">
-        <v>7.2771</v>
+        <v>7.2542</v>
       </c>
       <c r="X27" t="n">
-        <v>-10.778</v>
+        <v>-10.7518</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104739_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104739_W32.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.6311</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.4245</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.7991</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104739_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-10.7518</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
